--- a/天策评分卡/2026-09-11/导入_SC-B_小微企业经营评分卡.xlsx
+++ b/天策评分卡/2026-09-11/导入_SC-B_小微企业经营评分卡.xlsx
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
